--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,18 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangqijin/PycharmProjects/hangbo_2nd_v02/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B11B624-120D-3E46-9C27-924BF723D422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="46080" windowHeight="23680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="问卷数据" r:id="rId3" sheetId="1"/>
+    <sheet name="问卷数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">问卷数据!$A$1:$BS$75</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5325" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5325" uniqueCount="330">
   <si>
     <t>提交序号</t>
   </si>
@@ -1067,9 +1078,6 @@
     <t>2026-03-08 12:33:06</t>
   </si>
   <si>
-    <t>6. 其他-电商服务商</t>
-  </si>
-  <si>
     <t>4.46-55岁</t>
   </si>
   <si>
@@ -1103,34 +1111,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <u val="single"/>
-      <color indexed="12"/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="22"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1138,67 +1141,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin"/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin"/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -1213,111 +1162,400 @@
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BS75"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.24609375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="4.31640625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.22265625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.21875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="42.5" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="41.44921875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="37.96875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="27.28125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="27.28125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="27.28125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="27.28125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="27.28125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="29.48046875" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="29.48046875" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="29.48046875" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="29.48046875" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="29.48046875" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="28.37890625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="28.37890625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="28.37890625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="28.37890625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="28.37890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="33.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="33.3984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="33.3984375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="33.3984375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="44.68359375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="44.68359375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="46.40234375" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="49.0859375" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="47.984375" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="49.0859375" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="49.0859375" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="55.6875" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="36.8671875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="34.05078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="28.546875" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="61.1015625" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="5.1953125" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="20.515625" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="20.515625" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="3.24609375" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="7.64453125" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="9.3203125" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="10.41796875" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="7.64453125" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="5.4453125" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="5.4453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="48" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="34" bestFit="1" customWidth="1"/>
+    <col min="39" max="49" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="50" max="56" width="22" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="61.1640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="70" max="71" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:71">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,7 +1770,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:71">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -1747,7 +1985,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:71">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
@@ -1962,7 +2200,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:71">
       <c r="A4" s="2" t="s">
         <v>97</v>
       </c>
@@ -2177,7 +2415,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:71">
       <c r="A5" s="2" t="s">
         <v>102</v>
       </c>
@@ -2392,7 +2630,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:71">
       <c r="A6" s="2" t="s">
         <v>107</v>
       </c>
@@ -2607,7 +2845,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:71">
       <c r="A7" s="2" t="s">
         <v>111</v>
       </c>
@@ -2822,7 +3060,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:71">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -3037,7 +3275,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:71">
       <c r="A9" s="2" t="s">
         <v>118</v>
       </c>
@@ -3252,7 +3490,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:71">
       <c r="A10" s="2" t="s">
         <v>122</v>
       </c>
@@ -3467,7 +3705,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:71">
       <c r="A11" s="2" t="s">
         <v>125</v>
       </c>
@@ -3682,7 +3920,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:71">
       <c r="A12" s="2" t="s">
         <v>130</v>
       </c>
@@ -3897,7 +4135,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:71">
       <c r="A13" s="2" t="s">
         <v>133</v>
       </c>
@@ -4112,7 +4350,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:71">
       <c r="A14" s="2" t="s">
         <v>136</v>
       </c>
@@ -4327,7 +4565,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:71">
       <c r="A15" s="2" t="s">
         <v>139</v>
       </c>
@@ -4542,7 +4780,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:71">
       <c r="A16" s="2" t="s">
         <v>142</v>
       </c>
@@ -4757,7 +4995,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:71">
       <c r="A17" s="2" t="s">
         <v>146</v>
       </c>
@@ -4972,7 +5210,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:71">
       <c r="A18" s="2" t="s">
         <v>149</v>
       </c>
@@ -5187,7 +5425,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:71">
       <c r="A19" s="2" t="s">
         <v>152</v>
       </c>
@@ -5402,7 +5640,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:71">
       <c r="A20" s="2" t="s">
         <v>155</v>
       </c>
@@ -5617,7 +5855,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:71">
       <c r="A21" s="2" t="s">
         <v>158</v>
       </c>
@@ -5832,7 +6070,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:71">
       <c r="A22" s="2" t="s">
         <v>161</v>
       </c>
@@ -6047,7 +6285,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:71">
       <c r="A23" s="2" t="s">
         <v>165</v>
       </c>
@@ -6262,7 +6500,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:71">
       <c r="A24" s="2" t="s">
         <v>168</v>
       </c>
@@ -6477,7 +6715,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:71">
       <c r="A25" s="2" t="s">
         <v>171</v>
       </c>
@@ -6692,7 +6930,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:71">
       <c r="A26" s="2" t="s">
         <v>174</v>
       </c>
@@ -6907,7 +7145,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:71">
       <c r="A27" s="2" t="s">
         <v>178</v>
       </c>
@@ -7122,7 +7360,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:71">
       <c r="A28" s="2" t="s">
         <v>181</v>
       </c>
@@ -7337,7 +7575,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:71">
       <c r="A29" s="2" t="s">
         <v>184</v>
       </c>
@@ -7552,7 +7790,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:71">
       <c r="A30" s="2" t="s">
         <v>187</v>
       </c>
@@ -7767,7 +8005,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:71">
       <c r="A31" s="2" t="s">
         <v>191</v>
       </c>
@@ -7982,7 +8220,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:71">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -8197,7 +8435,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:71">
       <c r="A33" s="2" t="s">
         <v>202</v>
       </c>
@@ -8412,7 +8650,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:71">
       <c r="A34" s="2" t="s">
         <v>207</v>
       </c>
@@ -8627,7 +8865,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:71">
       <c r="A35" s="2" t="s">
         <v>210</v>
       </c>
@@ -8842,7 +9080,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:71">
       <c r="A36" s="2" t="s">
         <v>213</v>
       </c>
@@ -9057,7 +9295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:71">
       <c r="A37" s="2" t="s">
         <v>215</v>
       </c>
@@ -9272,7 +9510,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:71">
       <c r="A38" s="2" t="s">
         <v>218</v>
       </c>
@@ -9487,7 +9725,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:71">
       <c r="A39" s="2" t="s">
         <v>221</v>
       </c>
@@ -9702,7 +9940,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:71">
       <c r="A40" s="2" t="s">
         <v>224</v>
       </c>
@@ -9917,7 +10155,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:71">
       <c r="A41" s="2" t="s">
         <v>227</v>
       </c>
@@ -10132,7 +10370,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:71">
       <c r="A42" s="2" t="s">
         <v>230</v>
       </c>
@@ -10347,7 +10585,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:71">
       <c r="A43" s="2" t="s">
         <v>235</v>
       </c>
@@ -10562,7 +10800,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:71">
       <c r="A44" s="2" t="s">
         <v>238</v>
       </c>
@@ -10777,7 +11015,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:71">
       <c r="A45" s="2" t="s">
         <v>240</v>
       </c>
@@ -10992,7 +11230,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:71">
       <c r="A46" s="2" t="s">
         <v>242</v>
       </c>
@@ -11207,7 +11445,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:71">
       <c r="A47" s="2" t="s">
         <v>245</v>
       </c>
@@ -11422,7 +11660,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:71">
       <c r="A48" s="2" t="s">
         <v>248</v>
       </c>
@@ -11637,7 +11875,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:71">
       <c r="A49" s="2" t="s">
         <v>251</v>
       </c>
@@ -11852,7 +12090,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:71">
       <c r="A50" s="2" t="s">
         <v>254</v>
       </c>
@@ -12067,7 +12305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:71">
       <c r="A51" s="2" t="s">
         <v>258</v>
       </c>
@@ -12282,7 +12520,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:71">
       <c r="A52" s="2" t="s">
         <v>260</v>
       </c>
@@ -12497,7 +12735,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:71">
       <c r="A53" s="2" t="s">
         <v>263</v>
       </c>
@@ -12712,7 +12950,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:71">
       <c r="A54" s="2" t="s">
         <v>266</v>
       </c>
@@ -12927,7 +13165,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:71">
       <c r="A55" s="2" t="s">
         <v>269</v>
       </c>
@@ -13142,7 +13380,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:71">
       <c r="A56" s="2" t="s">
         <v>272</v>
       </c>
@@ -13357,7 +13595,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:71">
       <c r="A57" s="2" t="s">
         <v>275</v>
       </c>
@@ -13572,7 +13810,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:71">
       <c r="A58" s="2" t="s">
         <v>277</v>
       </c>
@@ -13787,7 +14025,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:71">
       <c r="A59" s="2" t="s">
         <v>280</v>
       </c>
@@ -14002,7 +14240,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:71">
       <c r="A60" s="2" t="s">
         <v>285</v>
       </c>
@@ -14217,7 +14455,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:71">
       <c r="A61" s="2" t="s">
         <v>290</v>
       </c>
@@ -14432,7 +14670,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:71">
       <c r="A62" s="2" t="s">
         <v>294</v>
       </c>
@@ -14647,7 +14885,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:71">
       <c r="A63" s="2" t="s">
         <v>299</v>
       </c>
@@ -14862,7 +15100,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:71">
       <c r="A64" s="2" t="s">
         <v>302</v>
       </c>
@@ -15077,7 +15315,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:71">
       <c r="A65" s="2" t="s">
         <v>82</v>
       </c>
@@ -15292,7 +15530,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:71">
       <c r="A66" s="2" t="s">
         <v>77</v>
       </c>
@@ -15507,7 +15745,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:71">
       <c r="A67" s="2" t="s">
         <v>80</v>
       </c>
@@ -15722,7 +15960,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:71">
       <c r="A68" s="2" t="s">
         <v>83</v>
       </c>
@@ -15937,7 +16175,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:71">
       <c r="A69" s="2" t="s">
         <v>104</v>
       </c>
@@ -16152,7 +16390,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:71">
       <c r="A70" s="2" t="s">
         <v>115</v>
       </c>
@@ -16367,7 +16605,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:71">
       <c r="A71" s="2" t="s">
         <v>196</v>
       </c>
@@ -16582,7 +16820,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:71">
       <c r="A72" s="2" t="s">
         <v>203</v>
       </c>
@@ -16590,16 +16828,16 @@
         <v>72</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>320</v>
+        <v>73</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>83</v>
@@ -16752,22 +16990,22 @@
         <v>76</v>
       </c>
       <c r="BE72" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="BF72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BG72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BH72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BI72" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="BF72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BH72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BI72" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="BJ72" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="BK72" s="2" t="s">
         <v>76</v>
@@ -16797,7 +17035,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:71">
       <c r="A73" s="2" t="s">
         <v>198</v>
       </c>
@@ -16814,7 +17052,7 @@
         <v>231</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>81</v>
@@ -16967,22 +17205,22 @@
         <v>76</v>
       </c>
       <c r="BE73" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="BF73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BG73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BH73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BI73" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="BF73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BH73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BI73" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="BJ73" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BK73" s="2" t="s">
         <v>76</v>
@@ -17012,7 +17250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:71">
       <c r="A74" s="2" t="s">
         <v>197</v>
       </c>
@@ -17194,10 +17432,10 @@
         <v>76</v>
       </c>
       <c r="BI74" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BJ74" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BK74" s="2" t="s">
         <v>76</v>
@@ -17227,7 +17465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:71">
       <c r="A75" s="2" t="s">
         <v>81</v>
       </c>
@@ -17244,7 +17482,7 @@
         <v>231</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>77</v>
@@ -17409,10 +17647,10 @@
         <v>76</v>
       </c>
       <c r="BI75" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BJ75" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BK75" s="2" t="s">
         <v>76</v>
@@ -17443,6 +17681,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>